--- a/testdata/CatalogData.xlsx
+++ b/testdata/CatalogData.xlsx
@@ -13,7 +13,6 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -792,7 +791,7 @@
         <v>33</v>
       </c>
       <c r="K2" s="4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>34</v>
